--- a/data/trans_camb/P1410-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1410-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,41</t>
+          <t>4,34</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>3,64</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,41</t>
+          <t>-2,85; 2,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,4</t>
+          <t>-4,81; 0,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 6,46</t>
+          <t>-0,42; 5,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,45</t>
+          <t>-0,92; 3,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 5,1</t>
+          <t>0,15; 5,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,63</t>
+          <t>2,22; 6,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,35</t>
+          <t>-1,2; 2,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,21</t>
+          <t>-1,37; 2,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,84</t>
+          <t>1,78; 5,55</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>41,24%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 26,92</t>
+          <t>-25,52; 33,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,54; 4,74</t>
+          <t>-43,09; 3,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 73,47</t>
+          <t>-3,88; 65,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 50,66</t>
+          <t>-9,67; 49,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 73,86</t>
+          <t>1,58; 78,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,67; 96,31</t>
+          <t>22,31; 101,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 29,81</t>
+          <t>-12,33; 27,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 26,16</t>
+          <t>-14,92; 25,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,16; 73,12</t>
+          <t>18,26; 69,57</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,93</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,69</t>
+          <t>-1,13; 0,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,01</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,77</t>
+          <t>0,88; 2,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,94</t>
+          <t>-0,69; 0,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,9</t>
+          <t>0,25; 1,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,27</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,53</t>
+          <t>-0,67; 0,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,67</t>
+          <t>0,38; 1,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,72</t>
+          <t>0,7; 2,0</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>101,67%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,06; 49,01</t>
+          <t>-47,1; 44,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 143,7</t>
+          <t>-0,46; 133,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 186,69</t>
+          <t>34,33; 211,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 108,98</t>
+          <t>-43,13; 104,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 212,43</t>
+          <t>12,57; 239,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 145,58</t>
+          <t>-0,55; 179,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,63; 39,27</t>
+          <t>-35,08; 40,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,56; 122,34</t>
+          <t>18,09; 127,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,19; 124,77</t>
+          <t>32,17; 151,84</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -0,58</t>
+          <t>-3,8; -0,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,92</t>
+          <t>-2,71; 0,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,33</t>
+          <t>-0,31; 3,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,92</t>
+          <t>-0,92; 0,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,86</t>
+          <t>0,19; 2,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,07</t>
+          <t>0,75; 3,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; -0,18</t>
+          <t>-2,14; -0,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,44</t>
+          <t>-1,1; 1,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,68</t>
+          <t>0,54; 2,84</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>416,94%</t>
+          <t>415,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>103,78%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-94,17; -13,37</t>
+          <t>-94,93; -23,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,39; 64,55</t>
+          <t>-76,28; 53,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 206,76</t>
+          <t>-10,86; 207,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1235,27 +1235,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,44; —</t>
+          <t>-41,51; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,04; —</t>
+          <t>12,03; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-91,41; -5,37</t>
+          <t>-90,15; -4,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 135,73</t>
+          <t>-47,48; 108,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,58; 255,17</t>
+          <t>20,36; 270,74</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,33</t>
+          <t>-1,73; 0,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,15</t>
+          <t>-1,68; 0,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,6</t>
+          <t>-0,14; 1,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,43</t>
+          <t>-0,62; 1,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,84</t>
+          <t>-0,27; 1,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,19</t>
+          <t>-0,36; 1,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,64</t>
+          <t>-0,85; 0,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,74</t>
+          <t>-0,74; 0,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,1</t>
+          <t>0,11; 1,41</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,24; 9,03</t>
+          <t>-34,41; 6,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 3,99</t>
+          <t>-33,44; 3,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 37,78</t>
+          <t>-3,04; 44,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 42,5</t>
+          <t>-14,06; 42,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 57,49</t>
+          <t>-6,6; 52,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 36,81</t>
+          <t>-8,34; 44,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,21; 17,13</t>
+          <t>-18,93; 14,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 19,69</t>
+          <t>-16,14; 17,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 28,11</t>
+          <t>2,54; 37,36</t>
         </is>
       </c>
     </row>
